--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Petugas_PROPORSI PERTANIAN NON PERTANIA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Petugas_PROPORSI PERTANIAN NON PERTANIA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,247 +429,247 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama Petugas</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email Petugas</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jabatan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha SE2026</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Target (ST2023)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Prelist</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Pertanian</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Persentase Pertanian</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Non Pertanian</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Pertanian​</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Persentase Pertanian​</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Non Pertanian​</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Pertanian​​</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Persentase Pertanian​​</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Non Pertanian​​</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Pertanian​​​</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Persentase Pertanian​​​</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Non Pertanian​​​</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
